--- a/travel_booking_forms/015_travel_request_booking_form--travel_booking_forms.xlsx
+++ b/travel_booking_forms/015_travel_request_booking_form--travel_booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_request_travel_agencies_other_hint</t>
+          <t>travel_request_travel_agencies_other_hint_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other Agency Hint</t>
+          <t>Travel Request Travel Agencies Other Hint 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>travel_request_travel_agency_hint</t>
+          <t>travel_request_travel_agency_hint_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Travel Agency Hint</t>
+          <t>Travel Request Travel Agency Hint 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>travel_request_destination_hint</t>
+          <t>travel_request_destination_hint_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Destination Hint</t>
+          <t>Travel Request Destination Hint 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>travel_request_number_of_guests_hint</t>
+          <t>travel_request_number_of_guests_hint_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Number of Guests Hint</t>
+          <t>Travel Request Number Of Guests Hint 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>travel_request_travel_type_hint</t>
+          <t>travel_request_travel_type_hint_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Travel Type Hint</t>
+          <t>Travel Request Travel Type Hint 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>travel_request_currency_hint</t>
+          <t>travel_request_currency_hint_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Currency Hint</t>
+          <t>Travel Request Currency Hint 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
